--- a/rad_pipeline/rpe1_ko_wt.xlsx
+++ b/rad_pipeline/rpe1_ko_wt.xlsx
@@ -84,7 +84,7 @@
     <t>r01c12</t>
   </si>
   <si>
-    <t>.001_original</t>
+    <t>0.001_original</t>
   </si>
   <si>
     <t>r02c11</t>
